--- a/upload/report/attandance_202402.xlsx
+++ b/upload/report/attandance_202402.xlsx
@@ -29,7 +29,7 @@
     <t>Created</t>
   </si>
   <si>
-    <t>2024-03-20 23:50:58</t>
+    <t>2024-03-21 10:32:53</t>
   </si>
   <si>
     <t>#</t>

--- a/upload/report/attandance_202402.xlsx
+++ b/upload/report/attandance_202402.xlsx
@@ -29,7 +29,7 @@
     <t>Created</t>
   </si>
   <si>
-    <t>2024-03-21 10:32:53</t>
+    <t>2024-03-25 17:05:46</t>
   </si>
   <si>
     <t>#</t>

--- a/upload/report/attandance_202402.xlsx
+++ b/upload/report/attandance_202402.xlsx
@@ -29,7 +29,7 @@
     <t>Created</t>
   </si>
   <si>
-    <t>2024-03-25 17:05:46</t>
+    <t>2024-03-26 18:02:17</t>
   </si>
   <si>
     <t>#</t>
